--- a/output/2026-10-11_17_Serbia_Sumadijski_ATEX_Equipment-Services.xlsx
+++ b/output/2026-10-11_17_Serbia_Sumadijski_ATEX_Equipment-Services.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Azienda di automazione industriale, rivenditore/integratore di apparecchiature Ex a marchio Pepperl+Fuchs per aree pericolose. Verificata tramite sito ufficiale attivo (pagina Kontakt), coerente con dati 2015. Nessun candidato trovato fisicamente in Sumadijski/Kragujevac: area allargata alla Serbia. Numero di cellulare alternativo trovato sul sito (+381 60 577 0 977) non riportato per evitare ambiguita.</t>
+          <t>Azienda di automazione industriale, rivenditore/integratore di apparecchiature Ex a marchio Pepperl+Fuchs per aree pericolose. Verificata tramite sito ufficiale attivo (pagina Kontakt), coerente con dati 2015. Nessun candidato trovato fisicamente in Sumadijski/Kragujevac: area allargata alla Serbia. Numero di cellulare alternativo trovato sul sito (+381 60 577 0 977) non riportato per evitare ambiguita. [DUPLICATO — vedi anche: 2026-10-10_10_Serbia_Podunavski_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -544,8 +544,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Ente di ispezione/certificazione ATEX/IECEx, partner di servizi B2B nel settore (non distributore di prodotti, non cliente finale). Verificato su pagine ufficiali sgs.com/en-rs. Telefono reperito solo da directory di terze parti (planplus.rs, non fonte ufficiale) quindi omesso; email non trovata. Nessun candidato trovato fisicamente in Sumadijski/Kragujevac: area allargata alla Serbia.</t>
